--- a/videos/002_inheritance_registration_neglect/image_generation_worklist.xlsx
+++ b/videos/002_inheritance_registration_neglect/image_generation_worklist.xlsx
@@ -561,11 +561,19 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing alone holding a smartphone to his ear late at night, stunned expression, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing alone holding a smartphone to his ear late at night, stunned expression, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -590,8 +598,16 @@
       <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, sitting exhausted at a low table at night with a phone pressed to her ear and a thick document folder in front of her, inside a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -619,8 +635,16 @@
       <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>close-up on a Japanese man's tense hand gripping a smartphone in a darkened room, knuckles pale, faint city light from a window, low-key desaturated ominous lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -648,11 +672,19 @@
       <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, turning his head slowly toward a leaning stack of sealed unopened envelopes on a small desk, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, turning his head slowly toward a leaning stack of sealed unopened envelopes on a small desk, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, low-key desaturated ominous lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -678,7 +710,11 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>extreme close-up on a pile of plain sealed envelopes buried under other mail at the edge of a desk, a thin layer of dust along the top edge, blank unmarked paper surfaces, low-key desaturated ominous lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -707,7 +743,11 @@
         <v>6</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, seen from the street at dusk with every window dark and unlit and an empty driveway, low-key desaturated ominous lighting, wide establishing shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -735,11 +775,19 @@
       <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, close-up on his face with lowered eyes and a slack guilty expression, blurred city night lights behind him, low-key desaturated ominous lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, close-up on his face with lowered eyes and a slack guilty expression, blurred city night lights behind him, low-key desaturated ominous lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -764,11 +812,19 @@
       <c r="D9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, working late at an office desk with two monitors, sleeves rolled up, a paper cup of coffee beside him, an open-plan Japanese office at night, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, working late at an office desk with two monitors, sleeves rolled up, a paper cup of coffee beside him, an open-plan Japanese office at night, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
@@ -793,11 +849,19 @@
       <c r="D10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, eating a convenience store meal alone at a small desk with his jacket still on, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, eating a convenience store meal alone at a small desk with his jacket still on, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -823,7 +887,11 @@
         <v>10</v>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, in gentle afternoon light with laundry drying by the entrance and a bicycle parked outside, warm natural saturation, soft daylight, wide establishing shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -851,8 +919,16 @@
       <c r="D12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, quietly pouring tea at a kitchen counter with her back half turned, an elderly Japanese woman in her late 70s seated at the low table behind her smiling, inside a modest Japanese family house, tatami room, sliding paper doors, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -861,7 +937,7 @@
       <c r="H12" s="8" t="inlineStr"/>
       <c r="I12" s="8" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>003</t>
@@ -880,11 +956,20 @@
       <c r="D13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png
+P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, wearing a black mourning suit, slim build, standing beside a Japanese woman in her mid 40s in a black mourning dress at a Buddhist memorial service, incense smoke rising before a family altar, tatami room, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, wearing a black mourning suit, slim build, standing beside a Japanese woman in her mid 40s in a black mourning dress at a Buddhist memorial service, incense smoke rising before a family altar, tatami room, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -909,8 +994,16 @@
       <c r="D14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, gathering used teacups onto a tray at a low table after the guests have left, floor cushions scattered around the room, inside a modest Japanese family house, tatami room, sliding paper doors, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -938,11 +1031,19 @@
       <c r="D15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, wearing a black mourning suit with the tie loosened, slim build, sitting cross-legged on tatami staring down at the floor mats with a distracted half-listening expression, inside a modest Japanese family house, tatami room, sliding paper doors, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, wearing a black mourning suit with the tie loosened, slim build, sitting cross-legged on tatami staring down at the floor mats with a distracted half-listening expression, inside a modest Japanese family house, tatami room, sliding paper doors, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -967,11 +1068,19 @@
       <c r="D16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, sitting alone on a bullet train seat looking out the window at passing countryside, a small overnight bag on the empty seat beside him, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, sitting alone on a bullet train seat looking out the window at passing countryside, a small overnight bag on the empty seat beside him, warm natural saturation, soft daylight, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -996,11 +1105,19 @@
       <c r="D17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, walking briskly down an office corridor with a phone held to his ear and a laptop under his arm, glancing at his wristwatch, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, walking briskly down an office corridor with a phone held to his ear and a laptop under his arm, glancing at his wristwatch, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1025,8 +1142,16 @@
       <c r="D18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, standing in a kitchen with a phone to her ear and her free hand resting on a stack of documents on the counter, a serious careful expression, inside a modest Japanese family house, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1054,11 +1179,19 @@
       <c r="D19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, pausing at a corridor window mid-call with a dismissive shrug and a light careless smile, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, pausing at a corridor window mid-call with a dismissive shrug and a light careless smile, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
@@ -1083,8 +1216,16 @@
       <c r="D20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, close-up on her face as she lowers the phone slightly, lips pressed together in a brief silence, gradually cooler tones, mild desaturation, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1112,8 +1253,16 @@
       <c r="D21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>an older Japanese man in his mid 60s, close-cropped grey hair, weathered face, zip-up work jacket over a polo shirt, sturdy build, sitting at a cluttered home table speaking firmly into a phone with a raised pointing finger, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1141,11 +1290,19 @@
       <c r="D22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing alone in an office stairwell holding the phone away from his ear with a vague uncomprehending expression, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing alone in an office stairwell holding the phone away from his ear with a vague uncomprehending expression, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr"/>
@@ -1170,11 +1327,19 @@
       <c r="D23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing in a crowded commuter train reading a message on his smartphone, other passengers blurred around him, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing in a crowded commuter train reading a message on his smartphone, other passengers blurred around him, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1199,11 +1364,19 @@
       <c r="D24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, slumped at a server room desk in the middle of the night surrounded by network equipment racks and blinking indicator lights, gradually cooler tones, mild desaturation, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, slumped at a server room desk in the middle of the night surrounded by network equipment racks and blinking indicator lights, gradually cooler tones, mild desaturation, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1229,7 +1402,11 @@
         <v>24</v>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>close-up on a plain sealed envelope resting on top of a shoe cabinet by a Japanese apartment entrance with house keys tossed beside it, blank unmarked paper surface, gradually cooler tones, mild desaturation, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1258,7 +1435,11 @@
         <v>25</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>close-up on the same plain sealed envelope now pushed to the edge of a desk and half buried under a growing pile of other mail and flyers, blank unmarked paper surfaces, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, gradually cooler tones, mild desaturation, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1286,11 +1467,19 @@
       <c r="D27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, sitting on the edge of his bed at night pressing a hand against his stomach as his phone lights up on the sheets beside him, an uneasy pained expression, in a compact modern Tokyo apartment room, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, sitting on the edge of his bed at night pressing a hand against his stomach as his phone lights up on the sheets beside him, an uneasy pained expression, in a compact modern Tokyo apartment room, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1315,8 +1504,16 @@
       <c r="D28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>extreme close-up on a man's thumb deliberately switching off a notification toggle on a smartphone in a dark room, the screen glow the only light source, blank interface surfaces with no readable content, gradually cooler tones, mild desaturation, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1345,7 +1542,11 @@
         <v>28</v>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, in harsh midsummer light with an overgrown garden and weathered roof tiles, gradually cooler tones, mild desaturation, wide establishing shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1373,8 +1574,16 @@
       <c r="D30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, sitting at a low table with a phone to her ear and an open estimate document and a calculator laid out before her, a composed but weary expression, inside a modest Japanese family house, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1403,7 +1612,11 @@
         <v>30</v>
       </c>
       <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>close-up on damaged roof tiles and a cracked rain gutter on an aged Japanese house, weeds sprouting from the gutter, gradually cooler tones, mild desaturation, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1431,11 +1644,19 @@
       <c r="D32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, leaning against a window with a phone to his ear and a relaxed unconcerned expression, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, leaning against a window with a phone to his ear and a relaxed unconcerned expression, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
@@ -1460,11 +1681,19 @@
       <c r="D33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, pulling open a desk drawer and looking down at a cheap ready-made name stamp lying among pens and cables, a faintly irritated expression, in a compact modern Tokyo apartment room, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, pulling open a desk drawer and looking down at a cheap ready-made name stamp lying among pens and cables, a faintly irritated expression, in a compact modern Tokyo apartment room, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr"/>
@@ -1489,11 +1718,19 @@
       <c r="D34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, shutting the drawer and turning back to his laptop instead with relaxed shoulders, the pile of unopened mail still beside him, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, shutting the drawer and turning back to his laptop instead with relaxed shoulders, the pile of unopened mail still beside him, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, gradually cooler tones, mild desaturation, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr"/>
@@ -1518,8 +1755,16 @@
       <c r="D35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, standing stiffly with a phone to her ear and a wall calendar behind her, tense shoulders, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1547,11 +1792,19 @@
       <c r="D36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, sitting bolt upright at his desk with the phone to his ear, eyes widening in dawning alarm, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, sitting bolt upright at his desk with the phone to his ear, eyes widening in dawning alarm, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1577,7 +1830,11 @@
         <v>36</v>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>close-up on an empty seal case lying open on a desk, a hollow velvet slot where a registered personal seal should be, blank unmarked surfaces, cold heavily desaturated low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1606,7 +1863,11 @@
         <v>37</v>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>the closed shutter of a Japanese city hall service counter seen from outside in the early evening, a dim empty waiting area with rows of vacant chairs behind the glass, cold heavily desaturated low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1634,11 +1895,19 @@
       <c r="D39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing in a crowded office war room during a system cutover with colleagues clustered around monitors behind him, his mouth half open as if unable to ask for time off, cold heavily desaturated low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing in a crowded office war room during a system cutover with colleagues clustered around monitors behind him, his mouth half open as if unable to ask for time off, cold heavily desaturated low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1663,8 +1932,16 @@
       <c r="D40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, close-up on her face during yet another phone call, her expression flattening into blank exhaustion, cold heavily desaturated low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1692,11 +1969,19 @@
       <c r="D41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, hunched over a laptop late at night placing a rush order for a personal seal, one hand pressed to his forehead, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, hunched over a laptop late at night placing a rush order for a personal seal, one hand pressed to his forehead, in a compact modern Tokyo apartment room, minimal furniture, a small desk with a laptop, city night view through the window, slightly cluttered with unopened mail, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -1721,11 +2006,19 @@
       <c r="D42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing motionless in a dark room after a call has ended, the phone lowered to his side, his face turned away from the light, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing motionless in a dark room after a call has ended, the phone lowered to his side, his face turned away from the light, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -1750,8 +2043,16 @@
       <c r="D43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
           <t>a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, sitting alone at a low table across from a real estate agent in a suit, quietly nodding in acceptance, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1779,11 +2080,19 @@
       <c r="D44" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, standing at the sliding entrance door of a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, an overnight bag in one hand, hesitating before stepping inside, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, standing at the sliding entrance door of a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, an overnight bag in one hand, hesitating before stepping inside, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr"/>
@@ -1809,7 +2118,11 @@
         <v>44</v>
       </c>
       <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
           <t>an emptied tatami room inside an old Japanese house with the closet doors slid open and the shelves bare, faint rectangular marks on the wall where furniture used to stand, cold heavily desaturated low-key dramatic lighting, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1837,11 +2150,19 @@
       <c r="D46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, kneeling at a low table and slowly opening a thick document binder with both hands, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, kneeling at a low table and slowly opening a thick document binder with both hands, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr"/>
@@ -1867,7 +2188,11 @@
         <v>46</v>
       </c>
       <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
           <t>extreme close-up on a small blank sticky note attached to the first page of an opened document binder, the paper slightly faded and curling at one corner, no legible writing on any surface, cold heavily desaturated low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -1895,11 +2220,19 @@
       <c r="D48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="8" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, close-up on his face staring down at the binder as realization breaks over him, eyes wide and then falling shut, cold heavily desaturated low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, close-up on his face staring down at the binder as realization breaks over him, eyes wide and then falling shut, cold heavily desaturated low-key dramatic lighting, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
@@ -1938,7 +2271,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" ht="28" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>008</t>
@@ -1957,11 +2290,20 @@
       <c r="D50" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="8" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png
+P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, sitting across a low table from a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, the woman giving a small faint smile as they mark dates on a calendar together, the man slightly taller than the woman, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, sitting across a low table from a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, the woman giving a small faint smile as they mark dates on a calendar together, the man slightly taller than the woman, inside a modest Japanese family house, cold heavily desaturated low-key dramatic lighting, medium shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -2218,7 +2560,11 @@
         <v>57</v>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOC01_apartment.png</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
           <t>an overhead flat-lay illustration of a desk calendar with one circled date, a personal seal and a certificate slip arranged in a neat diagonal row beside a single empty checkbox, flat vector style, clean calm neutral tones, high clarity, close-up shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
@@ -2227,7 +2573,7 @@
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr"/>
     </row>
-    <row r="59">
+    <row r="59" ht="28" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>011</t>
@@ -2246,11 +2592,20 @@
       <c r="D59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>P1_kawashima_takuya.png
+P2_kawashima_yuki.png</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOC02_family_house.png</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, business casual attire, slim build, and a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, standing side by side in front of a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, both looking calmly ahead in clear morning light, the man slightly taller than the woman, a single empty checkbox floating in the upper corner of the frame, clean calm neutral tones, high clarity, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
+          <t>a Japanese man in his early 40s, short neat black hair, tired eyes, light stubble, business casual attire, slim build, and a Japanese woman in her mid 40s, shoulder-length dark hair, practical cardigan over a blouse, average build, standing side by side in front of a modest Japanese family house in a quiet residential area, aged wooden exterior, small garden, traditional tiled roof, both looking calmly ahead in clear morning light, the man slightly taller than the woman, a single empty checkbox floating in the upper corner of the frame, clean calm neutral tones, high clarity, wide shot, manga anime style, cel shading, crisp clean linework, controlled color palette, absolutely no text, no letters, no words, no speech bubbles, no sound effects, no captions, no watermarks, no signatures, no UI elements in the image</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
